--- a/docs/준법확인프로젝트 테이블 정의서.xlsx
+++ b/docs/준법확인프로젝트 테이블 정의서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBDS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBDS\Documents\ComplianceOn\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5394C47-C04D-4723-B3DF-CCE2BD76D5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551F1557-24E5-4F8A-AAA1-23C535A87D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="93">
   <si>
     <t>순번</t>
   </si>
@@ -531,12 +531,27 @@
     <t>TB_COMP_EMP_ANS(직원별답변)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>IMG_FLNM</t>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMG_FLNM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지파일명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,6 +579,11 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="9">
@@ -616,7 +636,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -678,13 +698,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -739,15 +770,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -759,6 +781,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1294,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B4:K42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
     <col min="3" max="3" width="17.5" customWidth="1"/>
@@ -1304,31 +1344,31 @@
     <col min="11" max="11" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="2:7">
+      <c r="B4" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="F4" s="18" t="s">
+      <c r="C4" s="24"/>
+      <c r="F4" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" s="16" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:7">
       <c r="B6" s="10" t="s">
         <v>50</v>
       </c>
@@ -1342,7 +1382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7">
       <c r="B7" s="10" t="s">
         <v>52</v>
       </c>
@@ -1356,7 +1396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:7">
       <c r="B8" s="10" t="s">
         <v>54</v>
       </c>
@@ -1370,7 +1410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:7">
       <c r="B9" s="10" t="s">
         <v>87</v>
       </c>
@@ -1384,7 +1424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:7">
       <c r="B10" s="10" t="s">
         <v>23</v>
       </c>
@@ -1398,7 +1438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:7">
       <c r="B11" s="10" t="s">
         <v>33</v>
       </c>
@@ -1412,7 +1452,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:7">
       <c r="B12" s="10" t="s">
         <v>30</v>
       </c>
@@ -1426,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7">
       <c r="B13" s="10" t="s">
         <v>60</v>
       </c>
@@ -1434,7 +1474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:7">
       <c r="B14" s="10" t="s">
         <v>31</v>
       </c>
@@ -1442,13 +1482,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="F19" s="18" t="s">
+    <row r="19" spans="2:11">
+      <c r="F19" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:11">
       <c r="F20" s="12" t="s">
         <v>34</v>
       </c>
@@ -1456,7 +1496,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11">
       <c r="F21" s="14" t="s">
         <v>77</v>
       </c>
@@ -1464,33 +1504,33 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11">
       <c r="F22" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="2:11">
       <c r="F23" s="10" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="K23" s="21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11">
       <c r="F24" s="10" t="s">
         <v>33</v>
       </c>
@@ -1504,7 +1544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11">
       <c r="F25" s="10" t="s">
         <v>30</v>
       </c>
@@ -1518,7 +1558,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11">
       <c r="F26" s="10" t="s">
         <v>60</v>
       </c>
@@ -1532,11 +1572,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="18" t="s">
+    <row r="27" spans="2:11">
+      <c r="B27" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="18"/>
+      <c r="C27" s="23"/>
       <c r="F27" s="10" t="s">
         <v>31</v>
       </c>
@@ -1550,15 +1590,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11">
       <c r="B28" s="12" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="22"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
       <c r="J28" s="10" t="s">
         <v>76</v>
       </c>
@@ -1566,15 +1606,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11">
       <c r="B29" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
       <c r="J29" s="10" t="s">
         <v>62</v>
       </c>
@@ -1582,7 +1622,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11">
       <c r="B30" s="10" t="s">
         <v>39</v>
       </c>
@@ -1596,7 +1636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11">
       <c r="B31" s="10" t="s">
         <v>68</v>
       </c>
@@ -1610,12 +1650,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>70</v>
+    <row r="32" spans="2:11">
+      <c r="B32" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="J32" s="10" t="s">
         <v>30</v>
@@ -1624,12 +1664,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11">
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>60</v>
@@ -1638,12 +1678,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11">
       <c r="B34" s="10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J34" s="10" t="s">
         <v>31</v>
@@ -1652,24 +1692,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11">
       <c r="B35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C36" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="20"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>34</v>
@@ -1678,12 +1718,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11">
       <c r="B37" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>47</v>
@@ -1692,12 +1732,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11">
       <c r="B38" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>23</v>
@@ -1706,12 +1746,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11">
       <c r="B39" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>33</v>
@@ -1720,7 +1760,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11">
+      <c r="B40" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F40" s="10" t="s">
         <v>30</v>
       </c>
@@ -1728,7 +1774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11">
       <c r="F41" s="10" t="s">
         <v>60</v>
       </c>
@@ -1736,7 +1782,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11">
       <c r="F42" s="10" t="s">
         <v>31</v>
       </c>
@@ -1763,7 +1809,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
@@ -1775,7 +1821,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1804,7 +1850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1829,7 +1875,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1852,7 +1898,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1873,7 +1919,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1896,7 +1942,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1917,7 +1963,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1942,7 +1988,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1963,7 +2009,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1988,7 +2034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="17.25" thickBot="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2009,7 +2055,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="17.25" thickBot="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2043,7 +2089,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
@@ -2055,7 +2101,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2084,7 +2130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2109,7 +2155,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2130,7 +2176,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2151,7 +2197,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2176,7 +2222,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2197,7 +2243,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2222,7 +2268,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2243,7 +2289,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2277,8 +2323,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -2290,7 +2336,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +2365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2342,7 +2388,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2363,7 +2409,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2384,7 +2430,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2405,60 +2451,60 @@
       <c r="H5" s="5"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>70</v>
+      <c r="B6" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="27" customFormat="1" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2468,15 +2514,15 @@
       <c r="H8" s="1"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>27</v>
@@ -2486,102 +2532,123 @@
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" thickBot="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" thickBot="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" thickBot="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" thickBot="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2594,7 +2661,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -2606,7 +2673,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2635,7 +2702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2658,7 +2725,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2681,7 +2748,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2704,7 +2771,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2729,7 +2796,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2750,7 +2817,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2775,7 +2842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2796,7 +2863,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2830,7 +2897,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -2842,7 +2909,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2871,7 +2938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2892,7 +2959,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2917,7 +2984,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2942,7 +3009,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2963,7 +3030,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2988,7 +3055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3009,7 +3076,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3043,7 +3110,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -3055,7 +3122,7 @@
     <col min="9" max="9" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3084,7 +3151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3109,7 +3176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.25" thickBot="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3130,7 +3197,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3151,7 +3218,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.25" thickBot="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3176,7 +3243,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3199,7 +3266,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3220,7 +3287,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3241,7 +3308,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3266,7 +3333,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="17.25" thickBot="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3287,7 +3354,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="17.25" thickBot="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3312,7 +3379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="17.25" thickBot="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3333,7 +3400,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="17.25" thickBot="1">
       <c r="A13" s="3">
         <v>11</v>
       </c>
